--- a/Result/profitability/2444.xlsx
+++ b/Result/profitability/2444.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.31875</v>
+        <v>-0.38625</v>
       </c>
       <c r="N2" t="n">
-        <v>7.37625</v>
+        <v>4.32125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,16 +780,16 @@
         <v>-0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.32125</v>
+        <v>-0.44625</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2125</v>
+        <v>3.17125</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.33625</v>
+        <v>-0.41875</v>
       </c>
       <c r="N4" t="n">
-        <v>5.70625</v>
+        <v>3.16125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.01</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3125</v>
+        <v>-0.30375</v>
       </c>
       <c r="N5" t="n">
-        <v>6.2225</v>
+        <v>4.74375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.37</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.245</v>
+        <v>-0.2925</v>
       </c>
       <c r="N6" t="n">
-        <v>6.515</v>
+        <v>5.285</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.53</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.25375</v>
+        <v>-0.31375</v>
       </c>
       <c r="N7" t="n">
-        <v>6.74125</v>
+        <v>4.6575</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.22125</v>
+        <v>-0.2625</v>
       </c>
       <c r="N8" t="n">
-        <v>7.26125</v>
+        <v>5.84375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.225</v>
       </c>
       <c r="N9" t="n">
-        <v>7.581250000000001</v>
+        <v>7.58125</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>-0.185</v>
       </c>
       <c r="N11" t="n">
-        <v>7.91125</v>
+        <v>7.911249999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.24375</v>
       </c>
       <c r="N12" t="n">
-        <v>7.47</v>
+        <v>7.470000000000001</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2444</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>230</v>
+      </c>
+      <c r="D75" t="n">
+        <v>254</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-10.49</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-81</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-35.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-85</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.425</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.36125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6470588235294117</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-13.34117647058824</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07000000000000006</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.07692307692307698</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-11.83</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-8.828358208955223</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
